--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{EE419051-4E08-4B4D-8988-376DDF5F58D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B143CDD-E41D-4000-813F-1F89755095C6}"/>
+  <xr:revisionPtr revIDLastSave="745" documentId="8_{EE419051-4E08-4B4D-8988-376DDF5F58D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56C14477-7BD7-4355-9A02-4CE459B88D53}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1192.21875</v>
+        <v>29.808151483633502</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -473,7 +473,7 @@
       </c>
       <c r="B5">
         <f>B3/B4</f>
-        <v>12.397037037037038</v>
+        <v>495.83685214814858</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4347" documentId="8_{EE419051-4E08-4B4D-8988-376DDF5F58D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D631A57-EBD1-4A84-A433-32C40D55348C}"/>
+  <xr:revisionPtr revIDLastSave="13445" documentId="8_{EE419051-4E08-4B4D-8988-376DDF5F58D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{184369DF-9D5A-4047-8D00-CB0F5DB9E14E}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>
@@ -450,7 +450,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>73900.5650991</v>
+        <v>36949.949999999997</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -461,7 +461,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>662.34375</v>
+        <v>298.0546875</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -473,7 +473,7 @@
       </c>
       <c r="B5">
         <f>B3/B4</f>
-        <v>111.57433749333333</v>
+        <v>123.97037037037036</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="8_{EE419051-4E08-4B4D-8988-376DDF5F58D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DECAEF3-391A-4A98-8909-A6386E17DA38}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{602C0118-A9AE-4D86-9C46-D9EC5C6E3772}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -446,7 +446,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>36949.920440039998</v>
+        <v>31380</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -469,7 +469,7 @@
       </c>
       <c r="B5">
         <f>B3/B4</f>
-        <v>30.992567798518518</v>
+        <v>26.320673114728315</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{602C0118-A9AE-4D86-9C46-D9EC5C6E3772}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A53F9C38-6CD6-44CA-834A-1F472C709F59}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,6 +114,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,7 +450,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>31380</v>
+        <v>52300</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -457,7 +461,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1192.21875</v>
+        <v>1033.2562499999999</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -469,7 +473,7 @@
       </c>
       <c r="B5">
         <f>B3/B4</f>
-        <v>26.320673114728315</v>
+        <v>50.616679066785231</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A53F9C38-6CD6-44CA-834A-1F472C709F59}"/>
+  <xr:revisionPtr revIDLastSave="4010" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E46903-C7DA-4B73-B4A4-E0C50129F6E5}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4010" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E46903-C7DA-4B73-B4A4-E0C50129F6E5}"/>
+  <xr:revisionPtr revIDLastSave="5550" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C735F4B-35F9-4DD0-80D5-F14E05C4D283}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5550" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C735F4B-35F9-4DD0-80D5-F14E05C4D283}"/>
+  <xr:revisionPtr revIDLastSave="5608" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BA02C2D-A417-4E84-AF7B-D8632888C81E}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5608" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BA02C2D-A417-4E84-AF7B-D8632888C81E}"/>
+  <xr:revisionPtr revIDLastSave="6254" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EB1C121-B0A0-4367-AED2-4FF6D4319111}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>

--- a/Time_to_Cool/Time_to_Cool.xlsx
+++ b/Time_to_Cool/Time_to_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Time_to_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6254" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EB1C121-B0A0-4367-AED2-4FF6D4319111}"/>
+  <xr:revisionPtr revIDLastSave="8254" documentId="121_{0ACB61E9-0B16-4029-B598-CC8BB98DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0D905F1-F7F9-43DB-B762-8D5421CA9211}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{9B70E5BA-CDD1-43FB-AA4D-520C22E9AD9C}"/>
   </bookViews>
